--- a/clustered_sentences.xlsx
+++ b/clustered_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/peac-experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C892F763-C227-B245-8E08-E3876C4E418C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{EF80FF1F-3C4C-D043-AF69-973F10E68100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5540" yWindow="2300" windowWidth="27700" windowHeight="16940" xr2:uid="{A56C1C2B-3A0B-304A-84FE-95D49B9BBDCF}"/>
+    <workbookView xWindow="2540" yWindow="1480" windowWidth="27700" windowHeight="16940" xr2:uid="{A56C1C2B-3A0B-304A-84FE-95D49B9BBDCF}"/>
   </bookViews>
   <sheets>
     <sheet name="clustered_sentences" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="12766" uniqueCount="3113">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="12798" uniqueCount="3121">
   <si>
     <t>cluster_id</t>
   </si>
@@ -9387,6 +9387,30 @@
   </si>
   <si>
     <t>examples/analogy.yaml</t>
+  </si>
+  <si>
+    <t>examples/visual_resonance.yaml</t>
+  </si>
+  <si>
+    <t>format/skincare.yaml</t>
+  </si>
+  <si>
+    <t>tone/storyteller.yaml</t>
+  </si>
+  <si>
+    <t>markdown/markdown.yaml, markdown/bullet.yaml</t>
+  </si>
+  <si>
+    <t>tone/resilient.yaml</t>
+  </si>
+  <si>
+    <t>format/same.yaml</t>
+  </si>
+  <si>
+    <t>format/same.yaml,format/more_literary.yaml</t>
+  </si>
+  <si>
+    <t>examples/stories.yaml</t>
   </si>
 </sst>
 </file>
@@ -11580,6 +11604,9 @@
       <c r="D82" s="2" t="s">
         <v>2716</v>
       </c>
+      <c r="E82" s="1" t="s">
+        <v>3113</v>
+      </c>
     </row>
     <row r="83" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
@@ -11594,6 +11621,9 @@
       <c r="D83" s="2" t="s">
         <v>2720</v>
       </c>
+      <c r="E83" s="1" t="s">
+        <v>3113</v>
+      </c>
     </row>
     <row r="84" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
@@ -11608,6 +11638,9 @@
       <c r="D84" s="2" t="s">
         <v>2709</v>
       </c>
+      <c r="E84" s="1" t="s">
+        <v>3113</v>
+      </c>
     </row>
     <row r="85" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
@@ -11792,7 +11825,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>25</v>
       </c>
@@ -11806,7 +11839,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>25</v>
       </c>
@@ -11820,7 +11853,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>26</v>
       </c>
@@ -11834,7 +11867,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>26</v>
       </c>
@@ -11848,7 +11881,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>27</v>
       </c>
@@ -11862,7 +11895,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>27</v>
       </c>
@@ -11876,7 +11909,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>28</v>
       </c>
@@ -11889,8 +11922,11 @@
       <c r="D103" s="2" t="s">
         <v>2928</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E103" s="1" t="s">
+        <v>3114</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>28</v>
       </c>
@@ -11903,8 +11939,11 @@
       <c r="D104" s="2" t="s">
         <v>2924</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+      <c r="E104" s="1" t="s">
+        <v>3114</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>29</v>
       </c>
@@ -11918,7 +11957,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>29</v>
       </c>
@@ -11932,7 +11971,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>30</v>
       </c>
@@ -11946,7 +11985,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>30</v>
       </c>
@@ -11960,7 +11999,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>30</v>
       </c>
@@ -11974,7 +12013,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>31</v>
       </c>
@@ -11988,7 +12027,7 @@
         <v>1817</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>31</v>
       </c>
@@ -12002,7 +12041,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>32</v>
       </c>
@@ -12192,6 +12231,9 @@
       <c r="D124" s="2" t="s">
         <v>2506</v>
       </c>
+      <c r="E124" s="1" t="s">
+        <v>3115</v>
+      </c>
     </row>
     <row r="125" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
@@ -12206,6 +12248,9 @@
       <c r="D125" s="2" t="s">
         <v>2104</v>
       </c>
+      <c r="E125" s="1" t="s">
+        <v>3115</v>
+      </c>
     </row>
     <row r="126" spans="1:5" ht="20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
@@ -12237,6 +12282,9 @@
       <c r="D127" s="2" t="s">
         <v>2736</v>
       </c>
+      <c r="E127" s="1" t="s">
+        <v>3115</v>
+      </c>
     </row>
     <row r="128" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
@@ -12251,6 +12299,9 @@
       <c r="D128" s="2" t="s">
         <v>2101</v>
       </c>
+      <c r="E128" s="1" t="s">
+        <v>3115</v>
+      </c>
     </row>
     <row r="129" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
@@ -15340,6 +15391,9 @@
       <c r="D312" s="2" t="s">
         <v>364</v>
       </c>
+      <c r="E312" s="1" t="s">
+        <v>3075</v>
+      </c>
     </row>
     <row r="313" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
@@ -15354,6 +15408,9 @@
       <c r="D313" s="2" t="s">
         <v>456</v>
       </c>
+      <c r="E313" s="1" t="s">
+        <v>3116</v>
+      </c>
     </row>
     <row r="314" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
@@ -15687,6 +15744,9 @@
       <c r="D334" s="2" t="s">
         <v>2025</v>
       </c>
+      <c r="E334" s="1" t="s">
+        <v>3111</v>
+      </c>
       <c r="F334" s="1" t="s">
         <v>3105</v>
       </c>
@@ -15738,6 +15798,9 @@
       <c r="D337" s="2" t="s">
         <v>1860</v>
       </c>
+      <c r="E337" s="1" t="s">
+        <v>3081</v>
+      </c>
       <c r="F337" s="1" t="s">
         <v>3105</v>
       </c>
@@ -15772,6 +15835,9 @@
       <c r="D339" s="2" t="s">
         <v>2214</v>
       </c>
+      <c r="E339" s="1" t="s">
+        <v>3083</v>
+      </c>
     </row>
     <row r="340" spans="1:6" ht="40" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
@@ -16092,6 +16158,9 @@
       <c r="D358" s="2" t="s">
         <v>500</v>
       </c>
+      <c r="E358" s="1" t="s">
+        <v>3083</v>
+      </c>
     </row>
     <row r="359" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
@@ -16106,6 +16175,9 @@
       <c r="D359" s="2" t="s">
         <v>715</v>
       </c>
+      <c r="E359" s="1" t="s">
+        <v>3117</v>
+      </c>
     </row>
     <row r="360" spans="1:5" ht="40" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
@@ -16137,6 +16209,9 @@
       <c r="D361" s="2" t="s">
         <v>1679</v>
       </c>
+      <c r="E361" s="1" t="s">
+        <v>3117</v>
+      </c>
     </row>
     <row r="362" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
@@ -16179,6 +16254,9 @@
       <c r="D364" s="2" t="s">
         <v>2001</v>
       </c>
+      <c r="E364" s="1" t="s">
+        <v>3083</v>
+      </c>
     </row>
     <row r="365" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
@@ -16193,6 +16271,9 @@
       <c r="D365" s="2" t="s">
         <v>563</v>
       </c>
+      <c r="E365" s="1" t="s">
+        <v>3083</v>
+      </c>
     </row>
     <row r="366" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
@@ -16207,6 +16288,9 @@
       <c r="D366" s="2" t="s">
         <v>236</v>
       </c>
+      <c r="E366" s="1" t="s">
+        <v>3083</v>
+      </c>
     </row>
     <row r="367" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
@@ -16239,7 +16323,7 @@
         <v>3057</v>
       </c>
     </row>
-    <row r="369" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
         <v>68</v>
       </c>
@@ -16252,8 +16336,11 @@
       <c r="D369" s="2" t="s">
         <v>1261</v>
       </c>
-    </row>
-    <row r="370" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E369" s="1" t="s">
+        <v>3118</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
         <v>68</v>
       </c>
@@ -16266,8 +16353,11 @@
       <c r="D370" s="2" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="371" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E370" s="1" t="s">
+        <v>3119</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
         <v>69</v>
       </c>
@@ -16281,7 +16371,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="372" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
         <v>69</v>
       </c>
@@ -16294,8 +16384,11 @@
       <c r="D372" s="2" t="s">
         <v>2327</v>
       </c>
-    </row>
-    <row r="373" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E372" s="1" t="s">
+        <v>3057</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
         <v>69</v>
       </c>
@@ -16308,8 +16401,11 @@
       <c r="D373" s="2" t="s">
         <v>2592</v>
       </c>
-    </row>
-    <row r="374" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="E373" s="1" t="s">
+        <v>3057</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
         <v>72</v>
       </c>
@@ -16323,7 +16419,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="375" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
         <v>72</v>
       </c>
@@ -16337,7 +16433,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="376" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
         <v>72</v>
       </c>
@@ -16351,7 +16447,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="377" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
         <v>74</v>
       </c>
@@ -16365,7 +16461,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="378" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
         <v>74</v>
       </c>
@@ -16379,7 +16475,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="379" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
         <v>75</v>
       </c>
@@ -16393,7 +16489,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="380" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
         <v>75</v>
       </c>
@@ -16407,7 +16503,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="381" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
         <v>76</v>
       </c>
@@ -16421,7 +16517,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="382" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
         <v>76</v>
       </c>
@@ -16435,7 +16531,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="383" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
         <v>77</v>
       </c>
@@ -16449,7 +16545,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="384" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
         <v>78</v>
       </c>
@@ -16490,6 +16586,9 @@
       <c r="D386" s="2" t="s">
         <v>2350</v>
       </c>
+      <c r="E386" s="1" t="s">
+        <v>3083</v>
+      </c>
     </row>
     <row r="387" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
@@ -16504,6 +16603,9 @@
       <c r="D387" s="2" t="s">
         <v>1645</v>
       </c>
+      <c r="E387" s="1" t="s">
+        <v>3083</v>
+      </c>
     </row>
     <row r="388" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
@@ -16682,6 +16784,9 @@
       <c r="D398" s="2" t="s">
         <v>2551</v>
       </c>
+      <c r="E398" s="1" t="s">
+        <v>3080</v>
+      </c>
     </row>
     <row r="399" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
@@ -16696,6 +16801,9 @@
       <c r="D399" s="2" t="s">
         <v>759</v>
       </c>
+      <c r="E399" s="1" t="s">
+        <v>3080</v>
+      </c>
     </row>
     <row r="400" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
@@ -16710,8 +16818,11 @@
       <c r="D400" s="2" t="s">
         <v>2504</v>
       </c>
-    </row>
-    <row r="401" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+      <c r="E400" s="1" t="s">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
         <v>83</v>
       </c>
@@ -16725,7 +16836,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="402" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
         <v>83</v>
       </c>
@@ -16739,7 +16850,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="403" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
         <v>84</v>
       </c>
@@ -16753,7 +16864,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="404" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
         <v>84</v>
       </c>
@@ -16767,7 +16878,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="405" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
         <v>85</v>
       </c>
@@ -16781,7 +16892,7 @@
         <v>2612</v>
       </c>
     </row>
-    <row r="406" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
         <v>85</v>
       </c>
@@ -16795,7 +16906,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="407" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A407" s="1">
         <v>88</v>
       </c>
@@ -16809,7 +16920,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="408" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A408" s="1">
         <v>89</v>
       </c>
@@ -16822,8 +16933,11 @@
       <c r="D408" s="2" t="s">
         <v>2527</v>
       </c>
-    </row>
-    <row r="409" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+      <c r="E408" s="1" t="s">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A409" s="1">
         <v>89</v>
       </c>
@@ -16836,8 +16950,11 @@
       <c r="D409" s="2" t="s">
         <v>1698</v>
       </c>
-    </row>
-    <row r="410" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+      <c r="E409" s="1" t="s">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A410" s="1">
         <v>89</v>
       </c>
@@ -16850,8 +16967,11 @@
       <c r="D410" s="2" t="s">
         <v>1699</v>
       </c>
-    </row>
-    <row r="411" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E410" s="1" t="s">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A411" s="1">
         <v>90</v>
       </c>
@@ -16865,7 +16985,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="412" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A412" s="1">
         <v>90</v>
       </c>
@@ -16879,7 +16999,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="413" spans="1:4" ht="80" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:5" ht="80" x14ac:dyDescent="0.25">
       <c r="A413" s="1">
         <v>91</v>
       </c>
@@ -16893,7 +17013,7 @@
         <v>2887</v>
       </c>
     </row>
-    <row r="414" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A414" s="1">
         <v>91</v>
       </c>
@@ -16907,7 +17027,7 @@
         <v>2868</v>
       </c>
     </row>
-    <row r="415" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A415" s="1">
         <v>92</v>
       </c>
@@ -16921,7 +17041,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="416" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A416" s="1">
         <v>92</v>
       </c>

--- a/clustered_sentences.xlsx
+++ b/clustered_sentences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/peac-experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{EF80FF1F-3C4C-D043-AF69-973F10E68100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{D6008BDC-DE12-544E-BE89-5A9FD32742CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2540" yWindow="1480" windowWidth="27700" windowHeight="16940" xr2:uid="{A56C1C2B-3A0B-304A-84FE-95D49B9BBDCF}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="12798" uniqueCount="3121">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="12840" uniqueCount="3128">
   <si>
     <t>cluster_id</t>
   </si>
@@ -9412,12 +9412,33 @@
   <si>
     <t>examples/stories.yaml</t>
   </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>no_explanations.yaml</t>
+  </si>
+  <si>
+    <t>compact_explanation.yaml</t>
+  </si>
+  <si>
+    <t>compact.yaml</t>
+  </si>
+  <si>
+    <t>format/compact.yaml, format/engaging.yaml</t>
+  </si>
+  <si>
+    <t>exclude/no_speculation.yaml</t>
+  </si>
+  <si>
+    <t>knowledge/literacy.yaml</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -9548,6 +9569,13 @@
     <font>
       <sz val="14"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -9894,13 +9922,16 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -15265,6 +15296,9 @@
       <c r="D303" s="2" t="s">
         <v>2081</v>
       </c>
+      <c r="F303" s="1" t="s">
+        <v>3105</v>
+      </c>
     </row>
     <row r="304" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
@@ -15279,8 +15313,11 @@
       <c r="D304" s="2" t="s">
         <v>2070</v>
       </c>
-    </row>
-    <row r="305" spans="1:5" ht="40" x14ac:dyDescent="0.25">
+      <c r="F304" s="1" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>47</v>
       </c>
@@ -15293,8 +15330,11 @@
       <c r="D305" s="2" t="s">
         <v>2077</v>
       </c>
-    </row>
-    <row r="306" spans="1:5" ht="40" x14ac:dyDescent="0.25">
+      <c r="F305" s="3" t="s">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>47</v>
       </c>
@@ -15307,8 +15347,11 @@
       <c r="D306" s="2" t="s">
         <v>2071</v>
       </c>
-    </row>
-    <row r="307" spans="1:5" ht="40" x14ac:dyDescent="0.25">
+      <c r="F306" s="3" t="s">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>47</v>
       </c>
@@ -15321,8 +15364,11 @@
       <c r="D307" s="2" t="s">
         <v>2073</v>
       </c>
-    </row>
-    <row r="308" spans="1:5" ht="40" x14ac:dyDescent="0.25">
+      <c r="F307" s="3" t="s">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>48</v>
       </c>
@@ -15336,7 +15382,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="80" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" ht="80" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>48</v>
       </c>
@@ -15350,7 +15396,7 @@
         <v>2697</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="20" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>50</v>
       </c>
@@ -15364,7 +15410,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="20" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>50</v>
       </c>
@@ -15378,7 +15424,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>51</v>
       </c>
@@ -15395,7 +15441,7 @@
         <v>3075</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="40" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>51</v>
       </c>
@@ -15412,7 +15458,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="40" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>52</v>
       </c>
@@ -15426,7 +15472,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="20" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>52</v>
       </c>
@@ -15440,7 +15486,7 @@
         <v>2076</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="40" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>54</v>
       </c>
@@ -15457,7 +15503,7 @@
         <v>3109</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="40" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>54</v>
       </c>
@@ -15474,7 +15520,7 @@
         <v>3110</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" ht="20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>102</v>
       </c>
@@ -15491,7 +15537,7 @@
         <v>3057</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" ht="20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>102</v>
       </c>
@@ -15508,7 +15554,7 @@
         <v>3057</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" ht="20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>102</v>
       </c>
@@ -17334,6 +17380,9 @@
       <c r="D436" s="2" t="s">
         <v>566</v>
       </c>
+      <c r="E436" s="1" t="s">
+        <v>3057</v>
+      </c>
     </row>
     <row r="437" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A437" s="1">
@@ -17348,6 +17397,9 @@
       <c r="D437" s="2" t="s">
         <v>776</v>
       </c>
+      <c r="E437" s="1" t="s">
+        <v>3057</v>
+      </c>
     </row>
     <row r="438" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A438" s="1">
@@ -17362,6 +17414,9 @@
       <c r="D438" s="2" t="s">
         <v>776</v>
       </c>
+      <c r="E438" s="1" t="s">
+        <v>3057</v>
+      </c>
     </row>
     <row r="439" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A439" s="1">
@@ -17376,6 +17431,9 @@
       <c r="D439" s="2" t="s">
         <v>776</v>
       </c>
+      <c r="E439" s="1" t="s">
+        <v>3057</v>
+      </c>
     </row>
     <row r="440" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A440" s="1">
@@ -17432,6 +17490,9 @@
       <c r="D443" s="2" t="s">
         <v>69</v>
       </c>
+      <c r="E443" s="1" t="s">
+        <v>3122</v>
+      </c>
     </row>
     <row r="444" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A444" s="1">
@@ -17629,6 +17690,9 @@
       <c r="D456" s="2" t="s">
         <v>2106</v>
       </c>
+      <c r="E456" s="1" t="s">
+        <v>3122</v>
+      </c>
     </row>
     <row r="457" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A457" s="1">
@@ -17643,6 +17707,9 @@
       <c r="D457" s="2" t="s">
         <v>1959</v>
       </c>
+      <c r="E457" s="1" t="s">
+        <v>3122</v>
+      </c>
     </row>
     <row r="458" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A458" s="1">
@@ -17657,6 +17724,9 @@
       <c r="D458" s="2" t="s">
         <v>1943</v>
       </c>
+      <c r="E458" s="1" t="s">
+        <v>3122</v>
+      </c>
     </row>
     <row r="459" spans="1:5" ht="20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1">
@@ -18528,7 +18598,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="513" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A513" s="1">
         <v>117</v>
       </c>
@@ -18542,7 +18612,7 @@
         <v>2352</v>
       </c>
     </row>
-    <row r="514" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A514" s="1">
         <v>117</v>
       </c>
@@ -18556,7 +18626,7 @@
         <v>2348</v>
       </c>
     </row>
-    <row r="515" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A515" s="1">
         <v>118</v>
       </c>
@@ -18570,7 +18640,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="516" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A516" s="1">
         <v>118</v>
       </c>
@@ -18584,7 +18654,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="517" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A517" s="1">
         <v>120</v>
       </c>
@@ -18598,7 +18668,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="518" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A518" s="1">
         <v>120</v>
       </c>
@@ -18612,7 +18682,7 @@
         <v>2335</v>
       </c>
     </row>
-    <row r="519" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A519" s="1">
         <v>120</v>
       </c>
@@ -18626,7 +18696,7 @@
         <v>2331</v>
       </c>
     </row>
-    <row r="520" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A520" s="1">
         <v>122</v>
       </c>
@@ -18640,7 +18710,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="521" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A521" s="1">
         <v>122</v>
       </c>
@@ -18654,7 +18724,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="522" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A522" s="1">
         <v>123</v>
       </c>
@@ -18668,7 +18738,7 @@
         <v>2345</v>
       </c>
     </row>
-    <row r="523" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A523" s="1">
         <v>123</v>
       </c>
@@ -18682,7 +18752,7 @@
         <v>2341</v>
       </c>
     </row>
-    <row r="524" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A524" s="1">
         <v>124</v>
       </c>
@@ -18695,8 +18765,11 @@
       <c r="D524" s="2" t="s">
         <v>972</v>
       </c>
-    </row>
-    <row r="525" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E524" s="1" t="s">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A525" s="1">
         <v>124</v>
       </c>
@@ -18709,8 +18782,11 @@
       <c r="D525" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="526" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E525" s="1" t="s">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A526" s="1">
         <v>124</v>
       </c>
@@ -18723,8 +18799,11 @@
       <c r="D526" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="527" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E526" s="1" t="s">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A527" s="1">
         <v>124</v>
       </c>
@@ -18737,8 +18816,11 @@
       <c r="D527" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="528" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E527" s="1" t="s">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="528" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A528" s="1">
         <v>124</v>
       </c>
@@ -18750,6 +18832,9 @@
       </c>
       <c r="D528" s="2" t="s">
         <v>1322</v>
+      </c>
+      <c r="E528" s="1" t="s">
+        <v>3123</v>
       </c>
     </row>
     <row r="529" spans="1:5" ht="20" x14ac:dyDescent="0.25">
@@ -18765,6 +18850,9 @@
       <c r="D529" s="2" t="s">
         <v>1762</v>
       </c>
+      <c r="E529" s="1" t="s">
+        <v>3123</v>
+      </c>
     </row>
     <row r="530" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A530" s="1">
@@ -18779,6 +18867,9 @@
       <c r="D530" s="2" t="s">
         <v>2026</v>
       </c>
+      <c r="E530" s="1" t="s">
+        <v>3123</v>
+      </c>
     </row>
     <row r="531" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A531" s="1">
@@ -18793,6 +18884,9 @@
       <c r="D531" s="2" t="s">
         <v>1458</v>
       </c>
+      <c r="E531" s="1" t="s">
+        <v>3123</v>
+      </c>
     </row>
     <row r="532" spans="1:5" ht="20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
@@ -18909,6 +19003,9 @@
       <c r="D538" s="2" t="s">
         <v>819</v>
       </c>
+      <c r="E538" s="1" t="s">
+        <v>3123</v>
+      </c>
     </row>
     <row r="539" spans="1:5" ht="40" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="1">
@@ -19110,6 +19207,9 @@
       <c r="D550" s="2" t="s">
         <v>620</v>
       </c>
+      <c r="E550" s="1" t="s">
+        <v>3123</v>
+      </c>
     </row>
     <row r="551" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A551" s="1">
@@ -19251,7 +19351,7 @@
         <v>2913</v>
       </c>
     </row>
-    <row r="561" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A561" s="1">
         <v>128</v>
       </c>
@@ -19265,7 +19365,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="562" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A562" s="1">
         <v>129</v>
       </c>
@@ -19279,7 +19379,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="563" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A563" s="1">
         <v>129</v>
       </c>
@@ -19293,7 +19393,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="564" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A564" s="1">
         <v>130</v>
       </c>
@@ -19307,7 +19407,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="565" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A565" s="1">
         <v>130</v>
       </c>
@@ -19321,7 +19421,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="566" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A566" s="1">
         <v>131</v>
       </c>
@@ -19335,7 +19435,7 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="567" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A567" s="1">
         <v>131</v>
       </c>
@@ -19349,7 +19449,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="568" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A568" s="1">
         <v>133</v>
       </c>
@@ -19363,7 +19463,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="569" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A569" s="1">
         <v>133</v>
       </c>
@@ -19377,7 +19477,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="570" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A570" s="1">
         <v>134</v>
       </c>
@@ -19391,7 +19491,7 @@
         <v>2721</v>
       </c>
     </row>
-    <row r="571" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A571" s="1">
         <v>135</v>
       </c>
@@ -19404,8 +19504,11 @@
       <c r="D571" s="2" t="s">
         <v>2562</v>
       </c>
-    </row>
-    <row r="572" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E571" s="1" t="s">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="572" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A572" s="1">
         <v>135</v>
       </c>
@@ -19419,7 +19522,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="573" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A573" s="1">
         <v>136</v>
       </c>
@@ -19433,7 +19536,7 @@
         <v>2407</v>
       </c>
     </row>
-    <row r="574" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A574" s="1">
         <v>137</v>
       </c>
@@ -19447,7 +19550,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="575" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A575" s="1">
         <v>137</v>
       </c>
@@ -19461,7 +19564,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="576" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A576" s="1">
         <v>137</v>
       </c>
@@ -25836,7 +25939,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="993" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A993" s="1">
         <v>232</v>
       </c>
@@ -25850,7 +25953,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="994" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A994" s="1">
         <v>232</v>
       </c>
@@ -25864,7 +25967,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="995" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A995" s="1">
         <v>233</v>
       </c>
@@ -25878,7 +25981,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="996" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A996" s="1">
         <v>233</v>
       </c>
@@ -25892,7 +25995,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="997" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A997" s="1">
         <v>234</v>
       </c>
@@ -25906,7 +26009,7 @@
         <v>2602</v>
       </c>
     </row>
-    <row r="998" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A998" s="1">
         <v>235</v>
       </c>
@@ -25920,7 +26023,7 @@
         <v>2321</v>
       </c>
     </row>
-    <row r="999" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A999" s="1">
         <v>235</v>
       </c>
@@ -25934,7 +26037,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="1000" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1000" s="1">
         <v>235</v>
       </c>
@@ -25948,7 +26051,7 @@
         <v>2334</v>
       </c>
     </row>
-    <row r="1001" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A1001" s="1">
         <v>236</v>
       </c>
@@ -25962,7 +26065,7 @@
         <v>2883</v>
       </c>
     </row>
-    <row r="1002" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1002" s="1">
         <v>236</v>
       </c>
@@ -25976,7 +26079,7 @@
         <v>2871</v>
       </c>
     </row>
-    <row r="1003" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1003" s="1">
         <v>237</v>
       </c>
@@ -25990,7 +26093,7 @@
         <v>2641</v>
       </c>
     </row>
-    <row r="1004" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A1004" s="1">
         <v>238</v>
       </c>
@@ -26004,7 +26107,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="1005" spans="1:4" ht="80" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:5" ht="80" x14ac:dyDescent="0.25">
       <c r="A1005" s="1">
         <v>238</v>
       </c>
@@ -26018,7 +26121,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="1006" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1006" s="1">
         <v>239</v>
       </c>
@@ -26032,7 +26135,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="1007" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1007" s="1">
         <v>239</v>
       </c>
@@ -26045,8 +26148,11 @@
       <c r="D1007" s="2" t="s">
         <v>1922</v>
       </c>
-    </row>
-    <row r="1008" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E1007" s="1" t="s">
+        <v>3124</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1008" s="1">
         <v>239</v>
       </c>
@@ -26059,8 +26165,11 @@
       <c r="D1008" s="2" t="s">
         <v>2732</v>
       </c>
-    </row>
-    <row r="1009" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E1008" s="1" t="s">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1009" s="1">
         <v>240</v>
       </c>
@@ -26073,8 +26182,11 @@
       <c r="D1009" s="2" t="s">
         <v>1791</v>
       </c>
-    </row>
-    <row r="1010" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E1009" s="1" t="s">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1010" s="1">
         <v>240</v>
       </c>
@@ -26087,8 +26199,11 @@
       <c r="D1010" s="2" t="s">
         <v>2401</v>
       </c>
-    </row>
-    <row r="1011" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E1010" s="1" t="s">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1011" s="1">
         <v>240</v>
       </c>
@@ -26101,8 +26216,11 @@
       <c r="D1011" s="2" t="s">
         <v>2833</v>
       </c>
-    </row>
-    <row r="1012" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E1011" s="1" t="s">
+        <v>3124</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1012" s="1">
         <v>240</v>
       </c>
@@ -26115,8 +26233,11 @@
       <c r="D1012" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="1013" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E1012" s="1" t="s">
+        <v>3124</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1013" s="1">
         <v>240</v>
       </c>
@@ -26129,8 +26250,11 @@
       <c r="D1013" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="1014" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E1013" s="1" t="s">
+        <v>3124</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1014" s="1">
         <v>240</v>
       </c>
@@ -26143,8 +26267,11 @@
       <c r="D1014" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="1015" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E1014" s="1" t="s">
+        <v>3124</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1015" s="1">
         <v>241</v>
       </c>
@@ -26158,7 +26285,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="1016" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A1016" s="1">
         <v>241</v>
       </c>
@@ -26172,7 +26299,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="1017" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A1017" s="1">
         <v>241</v>
       </c>
@@ -26186,7 +26313,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="1018" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A1018" s="1">
         <v>242</v>
       </c>
@@ -26200,7 +26327,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="1019" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1019" s="1">
         <v>242</v>
       </c>
@@ -26213,8 +26340,11 @@
       <c r="D1019" s="2" t="s">
         <v>1539</v>
       </c>
-    </row>
-    <row r="1020" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E1019" s="1" t="s">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1020" s="1">
         <v>242</v>
       </c>
@@ -26227,8 +26357,11 @@
       <c r="D1020" s="2" t="s">
         <v>2962</v>
       </c>
-    </row>
-    <row r="1021" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E1020" s="1" t="s">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1021" s="1">
         <v>243</v>
       </c>
@@ -26242,7 +26375,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="1022" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1022" s="1">
         <v>243</v>
       </c>
@@ -26256,7 +26389,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="1023" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1023" s="1">
         <v>244</v>
       </c>
@@ -26270,7 +26403,7 @@
         <v>2931</v>
       </c>
     </row>
-    <row r="1024" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1024" s="1">
         <v>245</v>
       </c>
@@ -26541,6 +26674,9 @@
       <c r="D1042" s="2" t="s">
         <v>1011</v>
       </c>
+      <c r="E1042" s="1" t="s">
+        <v>3127</v>
+      </c>
     </row>
     <row r="1043" spans="1:5" ht="20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1043" s="1">
@@ -26572,6 +26708,9 @@
       <c r="D1044" s="2" t="s">
         <v>82</v>
       </c>
+      <c r="E1044" s="1" t="s">
+        <v>3127</v>
+      </c>
     </row>
     <row r="1045" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A1045" s="1">
@@ -44254,7 +44393,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2225" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2225" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2225" s="1">
         <v>833</v>
       </c>
@@ -44268,7 +44407,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="2226" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2226" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2226" s="1">
         <v>834</v>
       </c>
@@ -44282,7 +44421,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="2227" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2227" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2227" s="1">
         <v>835</v>
       </c>
@@ -44296,7 +44435,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="2228" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2228" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2228" s="1">
         <v>836</v>
       </c>
@@ -44310,7 +44449,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="2229" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2229" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2229" s="1">
         <v>837</v>
       </c>
@@ -44324,7 +44463,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="2230" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2230" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2230" s="1">
         <v>838</v>
       </c>
@@ -44338,7 +44477,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="2231" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="2231" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A2231" s="1">
         <v>839</v>
       </c>
@@ -44352,7 +44491,7 @@
         <v>2818</v>
       </c>
     </row>
-    <row r="2232" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="2232" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A2232" s="1">
         <v>840</v>
       </c>
@@ -44366,7 +44505,7 @@
         <v>2523</v>
       </c>
     </row>
-    <row r="2233" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="2233" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A2233" s="1">
         <v>840</v>
       </c>
@@ -44380,7 +44519,7 @@
         <v>2512</v>
       </c>
     </row>
-    <row r="2234" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2234" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2234" s="1">
         <v>842</v>
       </c>
@@ -44394,7 +44533,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="2235" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2235" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2235" s="1">
         <v>844</v>
       </c>
@@ -44408,7 +44547,7 @@
         <v>2466</v>
       </c>
     </row>
-    <row r="2236" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="2236" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A2236" s="1">
         <v>845</v>
       </c>
@@ -44422,7 +44561,7 @@
         <v>2607</v>
       </c>
     </row>
-    <row r="2237" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2237" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2237" s="1">
         <v>846</v>
       </c>
@@ -44436,7 +44575,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="2238" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2238" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2238" s="1">
         <v>847</v>
       </c>
@@ -44450,7 +44589,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="2239" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="2239" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A2239" s="1">
         <v>849</v>
       </c>
@@ -44463,8 +44602,11 @@
       <c r="D2239" s="2" t="s">
         <v>3021</v>
       </c>
-    </row>
-    <row r="2240" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="E2239" s="1" t="s">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2240" s="1">
         <v>850</v>
       </c>
@@ -50324,6 +50466,9 @@
       <c r="D2630" s="2" t="s">
         <v>2123</v>
       </c>
+      <c r="E2630" s="1" t="s">
+        <v>3126</v>
+      </c>
     </row>
     <row r="2631" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2631" s="1">
@@ -55021,7 +55166,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="2945" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="2945" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A2945" s="1">
         <v>1347</v>
       </c>
@@ -55035,7 +55180,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="2946" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="2946" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A2946" s="1">
         <v>1348</v>
       </c>
@@ -55049,7 +55194,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2947" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="2947" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A2947" s="1">
         <v>1349</v>
       </c>
@@ -55063,7 +55208,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="2948" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="2948" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A2948" s="1">
         <v>1350</v>
       </c>
@@ -55077,7 +55222,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="2949" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2949" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2949" s="1">
         <v>1351</v>
       </c>
@@ -55091,7 +55236,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="2950" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="2950" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A2950" s="1">
         <v>1352</v>
       </c>
@@ -55105,7 +55250,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="2951" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2951" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2951" s="1">
         <v>1353</v>
       </c>
@@ -55119,7 +55264,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="2952" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="2952" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A2952" s="1">
         <v>1354</v>
       </c>
@@ -55132,8 +55277,11 @@
       <c r="D2952" s="2" t="s">
         <v>2268</v>
       </c>
-    </row>
-    <row r="2953" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+      <c r="E2952" s="1" t="s">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="2953" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A2953" s="1">
         <v>1355</v>
       </c>
@@ -55147,7 +55295,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="2954" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2954" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2954" s="1">
         <v>1356</v>
       </c>
@@ -55161,7 +55309,7 @@
         <v>2747</v>
       </c>
     </row>
-    <row r="2955" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="2955" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A2955" s="1">
         <v>1357</v>
       </c>
@@ -55175,7 +55323,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="2956" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2956" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2956" s="1">
         <v>1358</v>
       </c>
@@ -55189,7 +55337,7 @@
         <v>2566</v>
       </c>
     </row>
-    <row r="2957" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2957" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2957" s="1">
         <v>1359</v>
       </c>
@@ -55203,7 +55351,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="2958" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="2958" spans="1:5" ht="40" x14ac:dyDescent="0.25">
       <c r="A2958" s="1">
         <v>1360</v>
       </c>
@@ -55217,7 +55365,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="2959" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2959" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2959" s="1">
         <v>1361</v>
       </c>
@@ -55231,7 +55379,7 @@
         <v>2275</v>
       </c>
     </row>
-    <row r="2960" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="2960" spans="1:5" ht="20" x14ac:dyDescent="0.25">
       <c r="A2960" s="1">
         <v>1362</v>
       </c>
@@ -61991,7 +62139,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="3409" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="3409" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A3409" s="1">
         <v>1682</v>
       </c>
@@ -62005,7 +62153,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="3410" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="3410" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A3410" s="1">
         <v>1683</v>
       </c>
@@ -62019,7 +62167,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3411" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="3411" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A3411" s="1">
         <v>1684</v>
       </c>
@@ -62033,7 +62181,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="3412" spans="1:4" ht="260" x14ac:dyDescent="0.25">
+    <row r="3412" spans="1:6" ht="260" x14ac:dyDescent="0.25">
       <c r="A3412" s="1">
         <v>1685</v>
       </c>
@@ -62047,7 +62195,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="3413" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="3413" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A3413" s="1">
         <v>1686</v>
       </c>
@@ -62061,7 +62209,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="3414" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="3414" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A3414" s="1">
         <v>1687</v>
       </c>
@@ -62075,7 +62223,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="3415" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="3415" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A3415" s="1">
         <v>1688</v>
       </c>
@@ -62089,7 +62237,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="3416" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="3416" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A3416" s="1">
         <v>1689</v>
       </c>
@@ -62103,7 +62251,7 @@
         <v>2126</v>
       </c>
     </row>
-    <row r="3417" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="3417" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A3417" s="1">
         <v>1690</v>
       </c>
@@ -62117,7 +62265,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="3418" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="3418" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A3418" s="1">
         <v>1691</v>
       </c>
@@ -62131,7 +62279,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="3419" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+    <row r="3419" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A3419" s="1">
         <v>1692</v>
       </c>
@@ -62145,7 +62293,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="3420" spans="1:4" ht="220" x14ac:dyDescent="0.25">
+    <row r="3420" spans="1:6" ht="220" x14ac:dyDescent="0.25">
       <c r="A3420" s="1">
         <v>1693</v>
       </c>
@@ -62158,8 +62306,11 @@
       <c r="D3420" s="2" t="s">
         <v>1653</v>
       </c>
-    </row>
-    <row r="3421" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+      <c r="F3420" s="1" t="s">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="3421" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A3421" s="1">
         <v>1694</v>
       </c>
@@ -62172,8 +62323,11 @@
       <c r="D3421" s="2" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="3422" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="F3421" s="1" t="s">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="3422" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A3422" s="1">
         <v>1695</v>
       </c>
@@ -62187,7 +62341,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="3423" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="3423" spans="1:6" ht="20" x14ac:dyDescent="0.25">
       <c r="A3423" s="1">
         <v>1696</v>
       </c>
@@ -62200,8 +62354,11 @@
       <c r="D3423" s="2" t="s">
         <v>1167</v>
       </c>
-    </row>
-    <row r="3424" spans="1:4" ht="40" x14ac:dyDescent="0.25">
+      <c r="F3423" s="1" t="s">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="3424" spans="1:6" ht="40" x14ac:dyDescent="0.25">
       <c r="A3424" s="1">
         <v>1697</v>
       </c>
